--- a/excel_project/部门考勤数据/深圳分公司 (Shenzhen Branch)_异常考勤数据.xlsx
+++ b/excel_project/部门考勤数据/深圳分公司 (Shenzhen Branch)_异常考勤数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>李超-Betty Li</t>
+          <t>陈岚-Cally Chen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,22 +478,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25-10-13 星期一</t>
+          <t>25-11-04 星期二</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>迟到</t>
+          <t>补卡审批通过</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>练文瑜-Liz Lian</t>
+          <t>陈岚-Cally Chen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25-10-14 星期二</t>
+          <t>25-11-12 星期三</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,17 +528,21 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>缺卡</t>
+          <t>补卡审批通过</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>练文瑜-Liz Lian</t>
+          <t>李超-Betty Li</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,18 +552,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25-10-15 星期三</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>25-10-22 星期三</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>缺卡</t>
+          <t>补卡审批通过</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -571,7 +579,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>梁斯琦-Suki Liang</t>
+          <t>李超-Betty Li</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -581,34 +589,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25-09-25 星期四</t>
+          <t>25-10-30 星期四</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>外勤</t>
+          <t>迟到</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>补卡审批通过</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>梁斯琦-Suki Liang</t>
+          <t>李超-Betty Li</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,22 +626,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25-10-09 星期四</t>
+          <t>25-11-03 星期一</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>补卡审批通过</t>
+          <t>迟到</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -645,7 +653,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>盘慧玲-Rebecca Pan</t>
+          <t>练文瑜-Liz Lian</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -655,34 +663,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25-09-23 星期二</t>
+          <t>25-10-21 星期二</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>外勤</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>补卡审批通过</t>
+          <t>管理员练文瑜-Liz Lian改为正常</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>盘慧玲-Rebecca Pan</t>
+          <t>练文瑜-Liz Lian</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -692,23 +700,316 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25-09-25 星期四</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>08:44</t>
-        </is>
-      </c>
+          <t>25-10-31 星期五</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>练文瑜-Liz Lian</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>深圳分公司 (Shenzhen Branch)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25-11-03 星期一</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>练文瑜-Liz Lian</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>深圳分公司 (Shenzhen Branch)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>25-11-04 星期二</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>练文瑜-Liz Lian</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>深圳分公司 (Shenzhen Branch)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>25-11-05 星期三</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>练文瑜-Liz Lian</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>深圳分公司 (Shenzhen Branch)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>25-11-06 星期四</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>练文瑜-Liz Lian</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>深圳分公司 (Shenzhen Branch)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>25-11-07 星期五</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>梁斯琦-Suki Liang</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>深圳分公司 (Shenzhen Branch)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>25-10-22 星期三</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>补卡审批通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>温咏仪-Winnie Wen</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>深圳分公司 (Shenzhen Branch)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>25-11-04 星期二</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>补卡审批通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>杨林栓-Young Yang</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>深圳分公司 (Shenzhen Branch)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>25-11-12 星期三</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>补卡审批通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>杨林栓-Young Yang</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>深圳分公司 (Shenzhen Branch)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>25-11-19 星期三</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>外勤</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>缺卡</t>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>补卡审批通过</t>
         </is>
       </c>
     </row>
